--- a/changes/9mm-barrels.xlsx
+++ b/changes/9mm-barrels.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABAFF7F-6609-4FD4-8374-43BA4DE042A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2EEEEA-549A-4790-84A6-85F1ED36F1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,37 +44,43 @@
     <t>pretty_name</t>
   </si>
   <si>
+    <t>ergonomics</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>horizontal_recoil</t>
+  </si>
+  <si>
+    <t>vertical_recoil</t>
+  </si>
+  <si>
+    <t>magazine_capacity</t>
+  </si>
+  <si>
+    <t>barrel_deviation</t>
+  </si>
+  <si>
+    <t>bullet_damage</t>
+  </si>
+  <si>
+    <t>bullet_velocity</t>
+  </si>
+  <si>
+    <t>buck_barrel_deviation</t>
+  </si>
+  <si>
+    <t>fire_rate</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
     <t>strength</t>
   </si>
   <si>
-    <t>ergonomics</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>horizontal_recoil</t>
-  </si>
-  <si>
-    <t>vertical_recoil</t>
-  </si>
-  <si>
-    <t>magazine_capacity</t>
-  </si>
-  <si>
-    <t>bullet_damage</t>
-  </si>
-  <si>
-    <t>bullet_velocity</t>
-  </si>
-  <si>
-    <t>buck_bullet_deviation</t>
-  </si>
-  <si>
-    <t>fire_rate</t>
-  </si>
-  <si>
-    <t>price</t>
+    <t>base</t>
   </si>
   <si>
     <t>length</t>
@@ -83,16 +89,160 @@
     <t>mod</t>
   </si>
   <si>
+    <t>dmg</t>
+  </si>
+  <si>
     <t>irl price</t>
   </si>
   <si>
-    <t>base</t>
-  </si>
-  <si>
-    <t>glock17_gen5_marksman_114mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t>114mm</t>
+    <t>kosch_9x19_114mm_barrel</t>
+  </si>
+  <si>
+    <t>KOSCH 9x19 114mm Barrel</t>
+  </si>
+  <si>
+    <t>sig_sauer_p320_compact_3.9inch_9x19_barrel</t>
+  </si>
+  <si>
+    <t>Sic Stürmer Compact-Size 3.9" 9x19</t>
+  </si>
+  <si>
+    <t>sig_sauer_p320_compact_4.6inch_threaded_9x19_barrel</t>
+  </si>
+  <si>
+    <t>Sic Stürmer Compact-Size 4.6" Threaded 9x19</t>
+  </si>
+  <si>
+    <t>sig_sauer_p320_full_4.7inch_9x19_barrel</t>
+  </si>
+  <si>
+    <t>Sic Stürmer Full-Size 4.7" 9x19</t>
+  </si>
+  <si>
+    <t>sig_sauer_p320_full_5.5inch_threaded_9x19_barrel</t>
+  </si>
+  <si>
+    <t>Sic Stürmer Full-Size 5.5" Threaded 9x19</t>
+  </si>
+  <si>
+    <t>whitner_defense_edc_x9_102mm_9x19_barrel</t>
+  </si>
+  <si>
+    <t>Whitner Defense EDC X9 102mm 9x19</t>
+  </si>
+  <si>
+    <t>whitner_defense_edc_x9_127mm_threaded_9x19_barrel</t>
+  </si>
+  <si>
+    <t>Whitner Defense EDC X9 127mm Threaded 9x19</t>
+  </si>
+  <si>
+    <t>hk_mp5_9x19_225mm_barrel</t>
+  </si>
+  <si>
+    <t>MPi-54 225mm 9x19</t>
+  </si>
+  <si>
+    <t>hk_mp5sd_9x19_146mm_barrel</t>
+  </si>
+  <si>
+    <t>MPi-54SD 146mm 9x19</t>
+  </si>
+  <si>
+    <t>bnb_value_line_light_tapered_melonite_ar9_76mm_9x19_barrel</t>
+  </si>
+  <si>
+    <t>KAK Value Line Light Tapered Melonite AR9 3" 9x19</t>
+  </si>
+  <si>
+    <t>cmmg_mk9_127mm_9x19_barrel</t>
+  </si>
+  <si>
+    <t>CmmG Mk9 5" 9x19</t>
+  </si>
+  <si>
+    <t>cmmg_mk9_216mm_9x19_barrel</t>
+  </si>
+  <si>
+    <t>CmmG Mk9 8.5" 9x19</t>
+  </si>
+  <si>
+    <t>cmmg_mk9_229mm_9x19_barrel</t>
+  </si>
+  <si>
+    <t>CmmG Mk9 9" 9x19</t>
+  </si>
+  <si>
+    <t>cmmg_mk9_406mm_9x19_c_barrel</t>
+  </si>
+  <si>
+    <t>CmmG Mk9 16" 9x19 Carbine Length</t>
+  </si>
+  <si>
+    <t>cmmg_mk9_406mm_9x19_m_barrel</t>
+  </si>
+  <si>
+    <t>CmmG Mk9 16" 9x19 Mid Length</t>
+  </si>
+  <si>
+    <t>cmmg_mk9_406mm_9x19_r_barrel</t>
+  </si>
+  <si>
+    <t>CmmG Mk9 16" 9x19 Rifle Length</t>
+  </si>
+  <si>
+    <t>kazarov_pp-19-01_238mm_9x19_barrel</t>
+  </si>
+  <si>
+    <t>Kazarov PP-19-01 Vityaz 238mm 9x19</t>
+  </si>
+  <si>
+    <t>kazarov_saiga_9_345mm_9x19_barrel</t>
+  </si>
+  <si>
+    <t>Kazarov Saiga-9 345mm 9x19</t>
+  </si>
+  <si>
+    <t>steyr_aug_para_9x19_420mm_barrel</t>
+  </si>
+  <si>
+    <t>Löwenherz AUG Para 9x19 420mm</t>
+  </si>
+  <si>
+    <t>steyr_aug_para_9x19_325mm_threaded_barrel</t>
+  </si>
+  <si>
+    <t>Löwenherz AUG Para 9x19 325mm Threaded</t>
+  </si>
+  <si>
+    <t>hk_ump9_200mm_flanged_barrel</t>
+  </si>
+  <si>
+    <t>UMC-9 200mm 9x19 Flanged</t>
+  </si>
+  <si>
+    <t>hk_ump9_200mm_trilug_threaded_barrel</t>
+  </si>
+  <si>
+    <t>UMC-9 200mm 9x19 Tri-Lug Threaded</t>
+  </si>
+  <si>
+    <t>vector_9mm_140mm_barrel</t>
+  </si>
+  <si>
+    <t>KALIS Scalar 9x19 140mm</t>
+  </si>
+  <si>
+    <t>vector_9mm_170mm_barrel</t>
+  </si>
+  <si>
+    <t>KALIS Scalar 9x19 170mm</t>
+  </si>
+  <si>
+    <t>radian_weapons_glock17_ramjet_barrel</t>
+  </si>
+  <si>
+    <t>Radian Weapons Glock 17 Gen5 RAMJET 9x19</t>
   </si>
   <si>
     <t>sai_match_threaded_9x19_barrel</t>
@@ -113,160 +263,10 @@
     <t>IGB Austria Match Grade Polygonal 406mm 9x19 Barrel</t>
   </si>
   <si>
-    <t>hk_mp5sd_9x19_146mm_barrel</t>
-  </si>
-  <si>
-    <t>HK MP5SD 9x19 146mm Barrel</t>
-  </si>
-  <si>
-    <t>hk_mp5_9x19_225mm_barrel</t>
-  </si>
-  <si>
-    <t>HK MP5 9x19 225mm Barrel</t>
-  </si>
-  <si>
-    <t>kak_value_line_light_tapered_melonite_ar9_76mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t>KAK Value Line Light Tapered Melonite AR9 3" 9x19</t>
-  </si>
-  <si>
-    <t>cmmg_mk9_216mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t>CmmG Mk9 8.5" 9x19</t>
-  </si>
-  <si>
-    <t>cmmg_mk9_229mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t>CmmG Mk9 9" 9x19</t>
-  </si>
-  <si>
-    <t>cmmg_mk9_406mm_9x19_c_barrel</t>
-  </si>
-  <si>
-    <t>CmmG Mk9 16" 9x19 Carbine Length</t>
-  </si>
-  <si>
-    <t>cmmg_mk9_406mm_9x19_r_barrel</t>
-  </si>
-  <si>
-    <t>CmmG Mk9 16" 9x19 Rifle Length</t>
-  </si>
-  <si>
-    <t>cmmg_mk9_406mm_9x19_m_barrel</t>
-  </si>
-  <si>
-    <t>CmmG Mk9 16" 9x19 Mid Length</t>
-  </si>
-  <si>
-    <t>cmmg_mk9_127mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t>CmmG Mk9 5" 9x19</t>
-  </si>
-  <si>
-    <t>steyr_aug_para_9x19_420mm_barrel</t>
-  </si>
-  <si>
-    <t>Steyr AUG Para 9x19 420mm</t>
-  </si>
-  <si>
-    <t>steyr_aug_para_9x19_325mm_threaded_barrel</t>
-  </si>
-  <si>
-    <t>Steyr AUG Para 9x19 325mm Threaded</t>
-  </si>
-  <si>
-    <t>hk_usc_419mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK USC 9x19 16.5" </t>
-  </si>
-  <si>
-    <t>radian_weapons_glock17_ramjet_barrel</t>
-  </si>
-  <si>
-    <t>Radian Weapons Glock 17 Gen5 RAMJET 9x19</t>
-  </si>
-  <si>
-    <t>barrel_deviation</t>
-  </si>
-  <si>
-    <t>vector_9mm_170mm_barrel</t>
-  </si>
-  <si>
-    <t>Kriss Vector 9x19 170mm</t>
-  </si>
-  <si>
-    <t>vector_9mm_140mm_barrel</t>
-  </si>
-  <si>
-    <t>Kriss Vector 9x19 140mm</t>
-  </si>
-  <si>
-    <t>izhmash_pp-19-01_238mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t>Izhmash PP-19-01 Vityaz 238mm 9x19</t>
-  </si>
-  <si>
-    <t>izhmash_saiga_9_345mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t>Izhmash Saiga-9 345mm 9x19</t>
-  </si>
-  <si>
-    <t>dmg</t>
-  </si>
-  <si>
-    <t>sig_sauer_p320_compact_3.9inch_9x19_barrel</t>
-  </si>
-  <si>
-    <t>Sig Sauer P320 Compact 3.9" 9x19 Barrel</t>
-  </si>
-  <si>
-    <t>sig_sauer_p320_compact_4.6inch_threaded_9x19_barrel</t>
-  </si>
-  <si>
-    <t>Sig Sauer P320 Compact 4.6" Threaded 9x19 Barrel</t>
-  </si>
-  <si>
-    <t>sig_sauer_p320_full_4.7inch_9x19_barrel</t>
-  </si>
-  <si>
-    <t>Sig Sauer P320 Full 4.7" 9x19 Barrel</t>
-  </si>
-  <si>
-    <t>sig_sauer_p320_full_5.5inch_threaded_9x19_barrel</t>
-  </si>
-  <si>
-    <t>Sig Sauer P320 Full 5.5" Threaded 9x19 Barrel</t>
-  </si>
-  <si>
-    <t>wilson_combat_edc_x9_102mm_9x19_barrel</t>
-  </si>
-  <si>
-    <t>Wilson Combat EDC X9 102mm 9x19</t>
-  </si>
-  <si>
-    <t>wilson_combat_edc_x9_127mm_threaded_9x19_barrel</t>
-  </si>
-  <si>
-    <t>Wilson Combat EDC X9 127mm Threaded 9x19</t>
-  </si>
-  <si>
-    <t>hk_ump9_200mm_flanged_barrel</t>
-  </si>
-  <si>
-    <t>HK UMP9 200mm 9x19 Flanged</t>
-  </si>
-  <si>
-    <t>hk_ump9_200mm_trilug_threaded_barrel</t>
-  </si>
-  <si>
-    <t>HK UMP9 200mm 9x19 Tri-Lug Threaded</t>
+    <t>kosch_10mm_114mm_barrel</t>
+  </si>
+  <si>
+    <t>KOSCH 10mm 114mm Barrel</t>
   </si>
 </sst>
 </file>
@@ -278,135 +278,99 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -458,13 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -481,13 +445,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -504,13 +468,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -527,13 +491,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -550,13 +514,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -573,13 +537,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -612,7 +576,7 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49995422223578601"/>
       </bottom>
       <diagonal/>
     </border>
@@ -754,48 +718,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Accent2" xfId="23" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent3" xfId="27" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Accent4" xfId="31" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent5" xfId="35" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent6" xfId="39" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - Accent1" xfId="20" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - Accent2" xfId="24" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - Accent3" xfId="28" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - Accent4" xfId="32" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - Accent5" xfId="36" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - Accent6" xfId="40" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - Accent1" xfId="21" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - Accent2" xfId="25" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - Accent3" xfId="29" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - Accent4" xfId="33" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - Accent5" xfId="37" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - Accent6" xfId="41" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Accent1" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Accent2" xfId="22" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Accent3" xfId="26" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Accent4" xfId="30" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Accent5" xfId="34" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Accent6" xfId="38" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Bad" xfId="7" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Calculation" xfId="11" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Check Cell" xfId="13" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Explanatory Text" xfId="16" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Good" xfId="6" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Heading 1" xfId="2" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Heading 2" xfId="3" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Heading 3" xfId="4" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Heading 4" xfId="5" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Input" xfId="9" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Linked Cell" xfId="12" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Neutral" xfId="8" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="15" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Output" xfId="10" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Title" xfId="1" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Total" xfId="17" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Warning Text" xfId="14" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -851,110 +815,16 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office 2013 - 2022">
@@ -966,23 +836,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -992,23 +862,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1016,26 +886,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1070,17 +937,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1097,17 +964,12 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
@@ -1127,22 +989,22 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>52</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -1160,42 +1022,42 @@
         <v>13</v>
       </c>
       <c r="N2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" t="s">
-        <v>15</v>
-      </c>
       <c r="T2" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="U2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E3">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1210,42 +1072,42 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>C3-D3*20-E3*0.8-F3*0.6-H3*7.5+I3*15+J3/300</f>
-        <v>13.596666666666666</v>
+        <f>C3-D3*20-E3*0.8-F3*0.6-H3*5+I3*10+J3/300+G3/1.3</f>
+        <v>-2.2033333333333331</v>
       </c>
       <c r="P3">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>4.4881900000000003</v>
       </c>
       <c r="S3">
-        <f>ROUND(Q3*0.028+P3+R3, 2)</f>
-        <v>0.16</v>
+        <f>ROUND(Q3*0.024+P3+R3,2)</f>
+        <v>0.11</v>
       </c>
       <c r="T3">
-        <f>(Q3-5)*0.09/11</f>
-        <v>-4.187536363636361E-3</v>
+        <f>ROUND((Q3-5)*0.09/11, 2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="D4">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E4">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>0.1</v>
@@ -1254,71 +1116,24 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>-57</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1500</v>
-      </c>
-      <c r="N4">
-        <f t="shared" ref="N4:N39" si="0">C4-D4*20-E4*0.8-F4*0.6-H4*7.5+I4*15+J4/300</f>
-        <v>11.66</v>
-      </c>
-      <c r="P4">
-        <v>0.03</v>
-      </c>
-      <c r="S4">
-        <f t="shared" ref="S4:S39" si="1">ROUND(Q4*0.028+P4+R4, 2)</f>
-        <v>0.03</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0.13</v>
-      </c>
-      <c r="E5">
-        <v>-7</v>
-      </c>
-      <c r="F5">
-        <v>-10</v>
-      </c>
-      <c r="H5">
-        <v>0.05</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>-57</v>
-      </c>
-      <c r="M5">
-        <v>1200</v>
-      </c>
       <c r="N5">
-        <f t="shared" si="0"/>
-        <v>8.4350000000000005</v>
-      </c>
-      <c r="P5">
-        <v>0.03</v>
-      </c>
-      <c r="Q5">
-        <v>4.5</v>
+        <f t="shared" ref="N5:N40" si="0">C5-D5*20-E5*0.8-F5*0.6-H5*7.5+I5*15+J5/300</f>
+        <v>0</v>
       </c>
       <c r="S5">
-        <f t="shared" si="1"/>
-        <v>0.16</v>
+        <f t="shared" ref="S5:S40" si="1">ROUND(Q5*0.024+P5+R5,2)</f>
+        <v>0</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T39" si="2">(Q5-5)*0.09/11</f>
-        <v>-4.0909090909090904E-3</v>
+        <f t="shared" ref="T5:T40" si="2">ROUND((Q5-5)*0.09/11, 2)</f>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1329,46 +1144,46 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="E6">
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="J6">
-        <v>-14</v>
+        <v>-80</v>
       </c>
       <c r="M6">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>15.353333333333333</v>
+        <v>-3.3166666666666664</v>
       </c>
       <c r="P6">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>6.0236200000000002</v>
+        <v>3.9</v>
       </c>
       <c r="S6">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="T6">
         <f t="shared" si="2"/>
-        <v>8.3750727272727272E-3</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -1379,177 +1194,174 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>-25</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>0.11</v>
       </c>
       <c r="E7">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>-0.2</v>
+        <v>0.05</v>
       </c>
       <c r="I7">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>140</v>
+        <v>-50</v>
       </c>
       <c r="M7">
         <v>3000</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>-12.683333333333334</v>
+        <v>-3.1416666666666666</v>
       </c>
       <c r="P7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>15.984252</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="S7">
         <f t="shared" si="1"/>
-        <v>0.48</v>
+        <v>0.11</v>
       </c>
       <c r="T7">
         <f t="shared" si="2"/>
-        <v>8.9871152727272724E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0.11</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>-45</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
       <c r="N8">
-        <f t="shared" ref="N8:N15" si="3">C8-D8*20-E8*0.8-F8*0.6-H8*7.5+I8*15+J8/300</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-2.35</v>
       </c>
       <c r="P8">
-        <v>0.03</v>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>4.7</v>
       </c>
       <c r="S8">
         <f t="shared" si="1"/>
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="T8">
-        <f t="shared" ref="T8:T15" si="4">(Q8-5)*0.09/11</f>
-        <v>-4.0909090909090902E-2</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="D9">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="I9">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="J9">
-        <v>-80</v>
+        <v>-10</v>
       </c>
       <c r="M9">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="N9">
-        <f t="shared" si="3"/>
-        <v>-4.666666666666667</v>
+        <f t="shared" ref="N9:N16" si="3">C9-D9*20-E9*0.8-F9*0.6-H9*5+I9*10+J9/300+G9/1.3</f>
+        <v>-3.5333333333333332</v>
       </c>
       <c r="P9">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="S9">
         <f t="shared" si="1"/>
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="T9">
-        <f t="shared" si="4"/>
-        <v>-9.0000000000000011E-3</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.13</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>0.05</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>-50</v>
-      </c>
-      <c r="M10">
-        <v>3000</v>
-      </c>
       <c r="N10">
         <f t="shared" si="3"/>
-        <v>-3.541666666666667</v>
-      </c>
-      <c r="P10">
-        <v>0.03</v>
-      </c>
-      <c r="Q10">
-        <v>4.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <f t="shared" si="1"/>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <f t="shared" si="4"/>
-        <v>-3.2727272727272757E-3</v>
+        <f t="shared" si="2"/>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1561,81 +1373,81 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>-45</v>
+        <v>-78</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
         <f t="shared" si="3"/>
-        <v>-2.8000000000000003</v>
+        <v>-2.2599999999999998</v>
       </c>
       <c r="P11">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>4.7</v>
+        <v>4.0157499999999997</v>
       </c>
       <c r="S11">
         <f t="shared" si="1"/>
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="T11">
-        <f t="shared" si="4"/>
-        <v>-2.4545454545454527E-3</v>
+        <f t="shared" si="2"/>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="C12">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D12">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="I12">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>-10</v>
+        <v>-44</v>
       </c>
       <c r="M12">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="N12">
         <f t="shared" si="3"/>
-        <v>-3.4833333333333338</v>
+        <v>-6.8466666666666667</v>
       </c>
       <c r="P12">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <f t="shared" si="1"/>
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="T12">
-        <f t="shared" si="4"/>
-        <v>4.0909090909090904E-3</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -1643,598 +1455,597 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P13">
-        <v>0.03</v>
-      </c>
       <c r="S13">
         <f t="shared" si="1"/>
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <f t="shared" si="4"/>
-        <v>-4.0909090909090902E-2</v>
+        <f t="shared" si="2"/>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J14">
-        <v>-78</v>
+        <v>47</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14">
         <f t="shared" si="3"/>
-        <v>-3.26</v>
+        <v>0.85666666666666713</v>
       </c>
       <c r="P14">
+        <v>0.04</v>
+      </c>
+      <c r="Q14">
+        <v>8.8582699999999992</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="2"/>
         <v>0.03</v>
-      </c>
-      <c r="Q14">
-        <v>4.0157499999999997</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="1"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="4"/>
-        <v>-8.0529545454545472E-3</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>0.22</v>
+      </c>
+      <c r="E15">
         <v>-1</v>
       </c>
-      <c r="D15">
-        <v>0.16</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
       <c r="F15">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="H15">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>-44</v>
+        <v>80</v>
       </c>
       <c r="M15">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="N15">
         <f t="shared" si="3"/>
-        <v>-7.8966666666666674</v>
+        <v>0.81666666666666621</v>
       </c>
       <c r="P15">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>5.74803</v>
       </c>
       <c r="S15">
         <f t="shared" si="1"/>
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="T15">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>0.01</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="N16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S16">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="2"/>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>0.31</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E17">
-        <v>-3</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>-7</v>
+        <v>8</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I17">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="J17">
-        <v>47</v>
+        <v>-300</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="N17">
         <f t="shared" si="0"/>
-        <v>1.006666666666667</v>
+        <v>-8.3250000000000011</v>
       </c>
       <c r="P17">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q17">
-        <v>8.8582699999999992</v>
+        <v>3</v>
       </c>
       <c r="S17">
         <f t="shared" si="1"/>
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="T17">
         <f t="shared" si="2"/>
-        <v>3.1567663636363624E-2</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>80</v>
+        <v>-225</v>
       </c>
       <c r="M18">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N18">
         <f t="shared" si="0"/>
-        <v>0.69166666666666621</v>
+        <v>-7.65</v>
       </c>
       <c r="P18">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q18">
-        <v>5.74803</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <f t="shared" si="1"/>
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="T18">
         <f t="shared" si="2"/>
-        <v>6.1202454545454541E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I19">
+        <v>0.03</v>
+      </c>
+      <c r="J19">
+        <v>-90</v>
+      </c>
+      <c r="M19">
+        <v>900</v>
       </c>
       <c r="N19">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-6.9750000000000005</v>
       </c>
       <c r="P19">
-        <v>0.06</v>
+        <v>0.04</v>
+      </c>
+      <c r="Q19">
+        <v>8.5</v>
       </c>
       <c r="S19">
         <f t="shared" si="1"/>
-        <v>0.06</v>
+        <v>0.24</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="2"/>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>0.14000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="I20">
-        <v>-0.15</v>
+        <v>0.04</v>
       </c>
       <c r="J20">
-        <v>-300</v>
+        <v>-70</v>
       </c>
       <c r="M20">
-        <v>750</v>
+        <v>950</v>
       </c>
       <c r="N20">
         <f t="shared" si="0"/>
-        <v>-10.125</v>
+        <v>-7.0083333333333346</v>
       </c>
       <c r="P20">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <f t="shared" si="1"/>
-        <v>0.14000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="T20">
         <f t="shared" si="2"/>
-        <v>-1.6363636363636361E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="D21">
-        <v>0.2</v>
+        <v>0.51</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="H21">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J21">
-        <v>-225</v>
+        <v>200</v>
       </c>
       <c r="M21">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <f t="shared" si="0"/>
-        <v>-7.65</v>
+        <v>-8.3833333333333346</v>
       </c>
       <c r="P21">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q21">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S21">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="T21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="D22">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="H22">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="J22">
-        <v>-90</v>
+        <v>200</v>
       </c>
       <c r="M22">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="N22">
         <f t="shared" si="0"/>
-        <v>-6.9750000000000005</v>
+        <v>-8.1833333333333336</v>
       </c>
       <c r="P22">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q22">
-        <v>8.5</v>
+        <v>16</v>
+      </c>
+      <c r="R22">
+        <v>0.01</v>
       </c>
       <c r="S22">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="T22">
         <f t="shared" si="2"/>
-        <v>2.8636363636363637E-2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="D23">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="H23">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="J23">
-        <v>-70</v>
+        <v>200</v>
       </c>
       <c r="M23">
-        <v>950</v>
+        <v>1200</v>
       </c>
       <c r="N23">
         <f t="shared" si="0"/>
-        <v>-7.0083333333333346</v>
+        <v>-7.9833333333333352</v>
       </c>
       <c r="P23">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q23">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="R23">
+        <v>0.02</v>
       </c>
       <c r="S23">
         <f t="shared" si="1"/>
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="T23">
         <f t="shared" si="2"/>
-        <v>3.2727272727272723E-2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24">
-        <v>-3</v>
-      </c>
-      <c r="D24">
-        <v>0.51</v>
-      </c>
-      <c r="E24">
-        <v>-2</v>
-      </c>
-      <c r="F24">
-        <v>-2</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0.09</v>
-      </c>
-      <c r="J24">
-        <v>200</v>
-      </c>
-      <c r="M24">
-        <v>1200</v>
-      </c>
       <c r="N24">
         <f t="shared" si="0"/>
-        <v>-8.3833333333333346</v>
-      </c>
-      <c r="P24">
-        <v>0.06</v>
-      </c>
-      <c r="Q24">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <f t="shared" si="1"/>
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="T24">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C25">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="E25">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I25">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="J25">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M25">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="N25">
         <f t="shared" si="0"/>
-        <v>-8.1833333333333336</v>
+        <v>-6.0083333333333337</v>
       </c>
       <c r="P25">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q25">
-        <v>16</v>
-      </c>
-      <c r="R25">
-        <v>0.01</v>
+        <v>9.3700799999999997</v>
       </c>
       <c r="S25">
         <f t="shared" si="1"/>
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="T25">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C26">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="D26">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="E26">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="F26">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J26">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="M26">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="N26">
         <f t="shared" si="0"/>
-        <v>-7.9833333333333352</v>
+        <v>-6.6500000000000021</v>
       </c>
       <c r="P26">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q26">
-        <v>16</v>
-      </c>
-      <c r="R26">
-        <v>0.02</v>
+        <v>13.582700000000001</v>
       </c>
       <c r="S26">
         <f t="shared" si="1"/>
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="T26">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -2242,112 +2053,113 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27">
-        <v>0.06</v>
-      </c>
       <c r="S27">
         <f t="shared" si="1"/>
-        <v>0.06</v>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="2"/>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
         <v>57</v>
       </c>
-      <c r="B28" t="s">
-        <v>58</v>
-      </c>
       <c r="C28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="H28">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="J28">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="N28">
         <f t="shared" si="0"/>
-        <v>-6.0083333333333337</v>
+        <v>12.433333333333334</v>
       </c>
       <c r="P28">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q28">
-        <v>9.3700799999999997</v>
+        <v>16.535399999999999</v>
       </c>
       <c r="S28">
         <f t="shared" si="1"/>
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="T28">
         <f t="shared" si="2"/>
-        <v>3.5755199999999994E-2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" t="s">
         <v>59</v>
       </c>
-      <c r="B29" t="s">
-        <v>60</v>
-      </c>
       <c r="C29">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="E29">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="F29">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I29">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="J29">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="M29">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="N29">
         <f t="shared" si="0"/>
-        <v>-6.6500000000000021</v>
+        <v>8.1</v>
       </c>
       <c r="P29">
+        <v>0.04</v>
+      </c>
+      <c r="Q29">
+        <v>12.795299999999999</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="2"/>
         <v>0.06</v>
-      </c>
-      <c r="Q29">
-        <v>13.582700000000001</v>
-      </c>
-      <c r="S29">
-        <f t="shared" si="1"/>
-        <v>0.44</v>
-      </c>
-      <c r="T29">
-        <f t="shared" si="2"/>
-        <v>7.0222090909090915E-2</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -2355,112 +2167,107 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P30">
-        <v>0.06</v>
-      </c>
       <c r="S30">
         <f t="shared" si="1"/>
-        <v>0.06</v>
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="2"/>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0.52</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E31">
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="F31">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31">
-        <v>0.09</v>
-      </c>
       <c r="J31">
-        <v>145</v>
+        <v>-15</v>
       </c>
       <c r="M31">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="N31">
         <f t="shared" si="0"/>
-        <v>12.433333333333334</v>
+        <v>-4.8500000000000005</v>
       </c>
       <c r="P31">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q31">
-        <v>16.535399999999999</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <f t="shared" si="1"/>
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="T31">
         <f t="shared" si="2"/>
-        <v>9.4380545454545439E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D32">
-        <v>0.42</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E32">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0.1</v>
-      </c>
-      <c r="I32">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="J32">
-        <v>105</v>
+        <v>-20</v>
       </c>
       <c r="M32">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="N32">
         <f t="shared" si="0"/>
-        <v>8.1</v>
+        <v>-9.4416666666666664</v>
       </c>
       <c r="P32">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q32">
-        <v>12.795299999999999</v>
+        <v>8</v>
       </c>
       <c r="S32">
         <f t="shared" si="1"/>
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="T32">
         <f t="shared" si="2"/>
-        <v>6.3779727272727266E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -2468,29 +2275,30 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P33">
-        <v>0.06</v>
-      </c>
       <c r="S33">
         <f t="shared" si="1"/>
-        <v>0.06</v>
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="2"/>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0.28000000000000003</v>
+        <v>0.23</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2498,249 +2306,302 @@
       <c r="H34">
         <v>0</v>
       </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
       <c r="J34">
-        <v>-15</v>
+        <v>-28</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="N34">
         <f t="shared" si="0"/>
-        <v>-4.8500000000000005</v>
+        <v>-4.6933333333333342</v>
       </c>
       <c r="P34">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q34">
-        <v>8</v>
+        <v>5.5118099999999997</v>
       </c>
       <c r="S34">
         <f t="shared" si="1"/>
-        <v>0.28000000000000003</v>
+        <v>0.17</v>
       </c>
       <c r="T34">
         <f t="shared" si="2"/>
-        <v>2.4545454545454547E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C35">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D35">
-        <v>0.28000000000000003</v>
+        <v>0.26</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H35">
-        <v>0.05</v>
+        <v>-0.05</v>
+      </c>
+      <c r="I35">
+        <v>0.02</v>
       </c>
       <c r="J35">
-        <v>-20</v>
+        <v>2</v>
+      </c>
+      <c r="K35">
+        <v>-0.1</v>
       </c>
       <c r="M35">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="N35">
         <f t="shared" si="0"/>
-        <v>-9.4416666666666664</v>
+        <v>-4.1183333333333341</v>
       </c>
       <c r="P35">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Q35">
-        <v>8</v>
+        <v>6.6929100000000004</v>
       </c>
       <c r="S35">
         <f t="shared" si="1"/>
-        <v>0.28000000000000003</v>
+        <v>0.2</v>
       </c>
       <c r="T35">
         <f t="shared" si="2"/>
-        <v>2.4545454545454547E-2</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36">
-        <v>-4</v>
-      </c>
-      <c r="D36">
-        <v>52</v>
-      </c>
-      <c r="E36">
-        <v>-3</v>
-      </c>
-      <c r="F36">
-        <v>-2</v>
-      </c>
-      <c r="H36">
-        <v>-0.1</v>
-      </c>
-      <c r="I36">
-        <v>0.09</v>
-      </c>
-      <c r="J36">
-        <v>275</v>
-      </c>
-      <c r="M36">
-        <v>1000</v>
-      </c>
       <c r="N36">
         <f t="shared" si="0"/>
-        <v>-1037.3833333333332</v>
-      </c>
-      <c r="P36">
-        <v>0.06</v>
-      </c>
-      <c r="Q36">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <f t="shared" si="1"/>
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="T36">
         <f t="shared" si="2"/>
-        <v>9.4090909090909086E-2</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>0.12</v>
+      </c>
+      <c r="E37">
+        <v>-10</v>
+      </c>
+      <c r="F37">
+        <v>-10</v>
+      </c>
+      <c r="H37">
+        <v>0.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>-57</v>
+      </c>
+      <c r="M37">
+        <v>1500</v>
+      </c>
       <c r="N37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11.66</v>
       </c>
       <c r="P37">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="S37">
         <f t="shared" si="1"/>
-        <v>0.06</v>
+        <v>0.03</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="2"/>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>-28</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
+        <v>-57</v>
       </c>
       <c r="M38">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="N38">
         <f t="shared" si="0"/>
-        <v>-4.6933333333333342</v>
+        <v>8.4350000000000005</v>
       </c>
       <c r="P38">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="Q38">
-        <v>5.5118099999999997</v>
+        <v>4.5</v>
       </c>
       <c r="S38">
         <f t="shared" si="1"/>
-        <v>0.21</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="T38">
         <f t="shared" si="2"/>
-        <v>4.187536363636361E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C39">
         <v>-1</v>
       </c>
       <c r="D39">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="H39">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="I39">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J39">
-        <v>2</v>
-      </c>
-      <c r="K39">
-        <v>-0.1</v>
+        <v>-14</v>
       </c>
       <c r="M39">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="N39">
         <f t="shared" si="0"/>
-        <v>-4.1183333333333341</v>
+        <v>15.353333333333333</v>
       </c>
       <c r="P39">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="Q39">
-        <v>6.6929100000000004</v>
+        <v>6.0236200000000002</v>
       </c>
       <c r="S39">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="T39">
         <f t="shared" si="2"/>
-        <v>1.385108181818182E-2</v>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40">
+        <v>-25</v>
+      </c>
+      <c r="D40">
+        <v>0.4</v>
+      </c>
+      <c r="E40">
+        <v>-10</v>
+      </c>
+      <c r="F40">
+        <v>-15</v>
+      </c>
+      <c r="H40">
+        <v>-0.2</v>
+      </c>
+      <c r="I40">
+        <v>0.09</v>
+      </c>
+      <c r="J40">
+        <v>140</v>
+      </c>
+      <c r="M40">
+        <v>3000</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="0"/>
+        <v>-12.683333333333334</v>
+      </c>
+      <c r="P40">
+        <v>0.03</v>
+      </c>
+      <c r="Q40">
+        <v>15.984252</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="1"/>
+        <v>0.41</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="2"/>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/changes/9mm-barrels.xlsx
+++ b/changes/9mm-barrels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2EEEEA-549A-4790-84A6-85F1ED36F1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60816E63-E791-45B7-BFF3-88F4534D7E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -714,8 +714,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -969,19 +970,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
     <col min="2" max="2" width="45.85546875" customWidth="1"/>
+    <col min="22" max="23" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1040,7 +1042,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1066,14 +1068,14 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>-61</v>
+        <v>-50</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
         <f>C3-D3*20-E3*0.8-F3*0.6-H3*5+I3*10+J3/300+G3/1.3</f>
-        <v>-2.2033333333333331</v>
+        <v>-2.1666666666666665</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1089,8 +1091,16 @@
         <f>ROUND((Q3-5)*0.09/11, 2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V3" s="1">
+        <f>(Q3-6)*35</f>
+        <v>-52.913349999999987</v>
+      </c>
+      <c r="W3" s="1">
+        <f>V3+1200</f>
+        <v>1147.08665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>76</v>
       </c>
@@ -1121,22 +1131,38 @@
       <c r="M4">
         <v>2000</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V4" s="1">
+        <f t="shared" ref="V4:V40" si="0">(Q4-6)*35</f>
+        <v>-210</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ref="W4:W40" si="1">V4+1200</f>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="N5">
-        <f t="shared" ref="N5:N40" si="0">C5-D5*20-E5*0.8-F5*0.6-H5*7.5+I5*15+J5/300</f>
+        <f t="shared" ref="N5:N40" si="2">C5-D5*20-E5*0.8-F5*0.6-H5*7.5+I5*15+J5/300</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f t="shared" ref="S5:S40" si="1">ROUND(Q5*0.024+P5+R5,2)</f>
+        <f t="shared" ref="S5:S40" si="3">ROUND(Q5*0.024+P5+R5,2)</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T40" si="2">ROUND((Q5-5)*0.09/11, 2)</f>
+        <f t="shared" ref="T5:T40" si="4">ROUND((Q5-5)*0.09/11, 2)</f>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V5" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1162,14 +1188,14 @@
         <v>-0.02</v>
       </c>
       <c r="J6">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="M6">
         <v>1000</v>
       </c>
       <c r="N6">
-        <f t="shared" si="0"/>
-        <v>-3.3166666666666664</v>
+        <f t="shared" si="2"/>
+        <v>-3.2833333333333332</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1178,15 +1204,23 @@
         <v>3.9</v>
       </c>
       <c r="S6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.09</v>
       </c>
       <c r="T6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.01</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V6" s="1">
+        <f t="shared" si="0"/>
+        <v>-73.5</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" si="1"/>
+        <v>1126.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1218,7 +1252,7 @@
         <v>3000</v>
       </c>
       <c r="N7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-3.1416666666666666</v>
       </c>
       <c r="P7">
@@ -1228,15 +1262,23 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="S7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.11</v>
       </c>
       <c r="T7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" si="0"/>
+        <v>-49.000000000000014</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" si="1"/>
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1262,14 +1304,14 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="0"/>
-        <v>-2.35</v>
+        <f t="shared" si="2"/>
+        <v>-2.3533333333333335</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1278,15 +1320,23 @@
         <v>4.7</v>
       </c>
       <c r="S8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.11</v>
       </c>
       <c r="T8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" si="0"/>
+        <v>-45.499999999999993</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" si="1"/>
+        <v>1154.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1312,14 +1362,14 @@
         <v>0.02</v>
       </c>
       <c r="J9">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="M9">
         <v>1500</v>
       </c>
       <c r="N9">
-        <f t="shared" ref="N9:N16" si="3">C9-D9*20-E9*0.8-F9*0.6-H9*5+I9*10+J9/300+G9/1.3</f>
-        <v>-3.5333333333333332</v>
+        <f t="shared" ref="N9:N16" si="5">C9-D9*20-E9*0.8-F9*0.6-H9*5+I9*10+J9/300+G9/1.3</f>
+        <v>-3.5666666666666669</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1328,29 +1378,45 @@
         <v>5.5</v>
       </c>
       <c r="S9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
       <c r="T9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" si="0"/>
+        <v>-17.5</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" si="1"/>
+        <v>1182.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="N10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V10" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1376,14 +1442,14 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>-78</v>
+        <v>-70</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <f t="shared" si="3"/>
-        <v>-2.2599999999999998</v>
+        <f t="shared" si="5"/>
+        <v>-2.2333333333333334</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1392,15 +1458,23 @@
         <v>4.0157499999999997</v>
       </c>
       <c r="S11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
       <c r="T11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.01</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V11" s="1">
+        <f t="shared" si="0"/>
+        <v>-69.448750000000004</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" si="1"/>
+        <v>1130.55125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1426,14 +1500,14 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="M12">
         <v>750</v>
       </c>
       <c r="N12">
-        <f t="shared" si="3"/>
-        <v>-6.8466666666666667</v>
+        <f t="shared" si="5"/>
+        <v>-6.8333333333333339</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1442,29 +1516,45 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" si="1"/>
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="N13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V13" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1490,14 +1580,14 @@
         <v>0.03</v>
       </c>
       <c r="J14">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="3"/>
-        <v>0.85666666666666713</v>
+        <f t="shared" si="5"/>
+        <v>1.0333333333333337</v>
       </c>
       <c r="P14">
         <v>0.04</v>
@@ -1506,15 +1596,23 @@
         <v>8.8582699999999992</v>
       </c>
       <c r="S14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
       <c r="T14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V14" s="1">
+        <f t="shared" si="0"/>
+        <v>100.03944999999997</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" si="1"/>
+        <v>1300.03945</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1546,7 +1644,7 @@
         <v>1000</v>
       </c>
       <c r="N15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.81666666666666621</v>
       </c>
       <c r="P15">
@@ -1556,29 +1654,45 @@
         <v>5.74803</v>
       </c>
       <c r="S15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
       <c r="T15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V15" s="1">
+        <f t="shared" si="0"/>
+        <v>-8.818950000000001</v>
+      </c>
+      <c r="W15" s="1">
+        <f t="shared" si="1"/>
+        <v>1191.1810499999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="N16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V16" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W16" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1604,14 +1718,14 @@
         <v>-0.03</v>
       </c>
       <c r="J17">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="M17">
         <v>750</v>
       </c>
       <c r="N17">
-        <f t="shared" si="0"/>
-        <v>-8.3250000000000011</v>
+        <f t="shared" si="2"/>
+        <v>-7.6583333333333341</v>
       </c>
       <c r="P17">
         <v>0.04</v>
@@ -1620,15 +1734,23 @@
         <v>3</v>
       </c>
       <c r="S17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.11</v>
       </c>
       <c r="T17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.02</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V17" s="1">
+        <f t="shared" si="0"/>
+        <v>-105</v>
+      </c>
+      <c r="W17" s="1">
+        <f t="shared" si="1"/>
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1654,14 +1776,14 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>-225</v>
+        <v>-40</v>
       </c>
       <c r="M18">
         <v>800</v>
       </c>
       <c r="N18">
-        <f t="shared" si="0"/>
-        <v>-7.65</v>
+        <f t="shared" si="2"/>
+        <v>-7.0333333333333341</v>
       </c>
       <c r="P18">
         <v>0.04</v>
@@ -1670,15 +1792,23 @@
         <v>5</v>
       </c>
       <c r="S18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
       <c r="T18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="W18" s="1">
+        <f t="shared" si="1"/>
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1704,14 +1834,14 @@
         <v>0.03</v>
       </c>
       <c r="J19">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="M19">
         <v>900</v>
       </c>
       <c r="N19">
-        <f t="shared" si="0"/>
-        <v>-6.9750000000000005</v>
+        <f t="shared" si="2"/>
+        <v>-6.3750000000000009</v>
       </c>
       <c r="P19">
         <v>0.04</v>
@@ -1720,15 +1850,23 @@
         <v>8.5</v>
       </c>
       <c r="S19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.24</v>
       </c>
       <c r="T19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V19" s="1">
+        <f t="shared" si="0"/>
+        <v>87.5</v>
+      </c>
+      <c r="W19" s="1">
+        <f t="shared" si="1"/>
+        <v>1287.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1754,14 +1892,14 @@
         <v>0.04</v>
       </c>
       <c r="J20">
-        <v>-70</v>
+        <v>110</v>
       </c>
       <c r="M20">
         <v>950</v>
       </c>
       <c r="N20">
-        <f t="shared" si="0"/>
-        <v>-7.0083333333333346</v>
+        <f t="shared" si="2"/>
+        <v>-6.408333333333335</v>
       </c>
       <c r="P20">
         <v>0.04</v>
@@ -1770,15 +1908,23 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.26</v>
       </c>
       <c r="T20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V20" s="1">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="W20" s="1">
+        <f t="shared" si="1"/>
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1810,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-8.3833333333333346</v>
       </c>
       <c r="P21">
@@ -1820,15 +1966,23 @@
         <v>16</v>
       </c>
       <c r="S21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.42</v>
       </c>
       <c r="T21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.09</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V21" s="1">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="W21" s="1">
+        <f t="shared" si="1"/>
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -1860,7 +2014,7 @@
         <v>1200</v>
       </c>
       <c r="N22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-8.1833333333333336</v>
       </c>
       <c r="P22">
@@ -1873,15 +2027,23 @@
         <v>0.01</v>
       </c>
       <c r="S22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.43</v>
       </c>
       <c r="T22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.09</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V22" s="1">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="W22" s="1">
+        <f t="shared" si="1"/>
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1913,7 +2075,7 @@
         <v>1200</v>
       </c>
       <c r="N23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-7.9833333333333352</v>
       </c>
       <c r="P23">
@@ -1926,29 +2088,45 @@
         <v>0.02</v>
       </c>
       <c r="S23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.44</v>
       </c>
       <c r="T23">
+        <f t="shared" si="4"/>
+        <v>0.09</v>
+      </c>
+      <c r="V23" s="1">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="W23" s="1">
+        <f t="shared" si="1"/>
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N24">
         <f t="shared" si="2"/>
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="N24">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V24" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W24" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1974,14 +2152,14 @@
         <v>0.04</v>
       </c>
       <c r="J25">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <f t="shared" si="0"/>
-        <v>-6.0083333333333337</v>
+        <f t="shared" si="2"/>
+        <v>-5.7750000000000004</v>
       </c>
       <c r="P25">
         <v>0.04</v>
@@ -1990,15 +2168,23 @@
         <v>9.3700799999999997</v>
       </c>
       <c r="S25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.26</v>
       </c>
       <c r="T25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.04</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V25" s="1">
+        <f t="shared" si="0"/>
+        <v>117.9528</v>
+      </c>
+      <c r="W25" s="1">
+        <f t="shared" si="1"/>
+        <v>1317.9528</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -2024,14 +2210,14 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="J26">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="M26">
         <v>500</v>
       </c>
       <c r="N26">
-        <f t="shared" si="0"/>
-        <v>-6.6500000000000021</v>
+        <f t="shared" si="2"/>
+        <v>-6.3833333333333355</v>
       </c>
       <c r="P26">
         <v>0.04</v>
@@ -2040,29 +2226,45 @@
         <v>13.582700000000001</v>
       </c>
       <c r="S26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
       <c r="T26">
+        <f t="shared" si="4"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="V26" s="1">
+        <f t="shared" si="0"/>
+        <v>265.39450000000005</v>
+      </c>
+      <c r="W26" s="1">
+        <f t="shared" si="1"/>
+        <v>1465.3945000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N27">
         <f t="shared" si="2"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="N27">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V27" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W27" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -2088,14 +2290,14 @@
         <v>0.09</v>
       </c>
       <c r="J28">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="M28">
         <v>2000</v>
       </c>
       <c r="N28">
-        <f t="shared" si="0"/>
-        <v>12.433333333333334</v>
+        <f t="shared" si="2"/>
+        <v>12.616666666666667</v>
       </c>
       <c r="P28">
         <v>0.04</v>
@@ -2104,15 +2306,23 @@
         <v>16.535399999999999</v>
       </c>
       <c r="S28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.44</v>
       </c>
       <c r="T28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.09</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V28" s="1">
+        <f t="shared" si="0"/>
+        <v>368.73899999999998</v>
+      </c>
+      <c r="W28" s="1">
+        <f t="shared" si="1"/>
+        <v>1568.739</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -2138,14 +2348,14 @@
         <v>0.06</v>
       </c>
       <c r="J29">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="M29">
         <v>3000</v>
       </c>
       <c r="N29">
-        <f t="shared" si="0"/>
-        <v>8.1</v>
+        <f t="shared" si="2"/>
+        <v>8.2833333333333332</v>
       </c>
       <c r="P29">
         <v>0.04</v>
@@ -2154,29 +2364,45 @@
         <v>12.795299999999999</v>
       </c>
       <c r="S29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.35</v>
       </c>
       <c r="T29">
+        <f t="shared" si="4"/>
+        <v>0.06</v>
+      </c>
+      <c r="V29" s="1">
+        <f t="shared" si="0"/>
+        <v>237.83549999999997</v>
+      </c>
+      <c r="W29" s="1">
+        <f t="shared" si="1"/>
+        <v>1437.8354999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N30">
         <f t="shared" si="2"/>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="N30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V30" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W30" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -2199,14 +2425,14 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>-15</v>
+        <v>70</v>
       </c>
       <c r="M31">
         <v>500</v>
       </c>
       <c r="N31">
-        <f t="shared" si="0"/>
-        <v>-4.8500000000000005</v>
+        <f t="shared" si="2"/>
+        <v>-4.5666666666666673</v>
       </c>
       <c r="P31">
         <v>0.04</v>
@@ -2215,15 +2441,23 @@
         <v>8</v>
       </c>
       <c r="S31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.23</v>
       </c>
       <c r="T31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.02</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V31" s="1">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="W31" s="1">
+        <f t="shared" si="1"/>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -2246,14 +2480,14 @@
         <v>0.05</v>
       </c>
       <c r="J32">
-        <v>-20</v>
+        <v>70</v>
       </c>
       <c r="M32">
         <v>1000</v>
       </c>
       <c r="N32">
-        <f t="shared" si="0"/>
-        <v>-9.4416666666666664</v>
+        <f t="shared" si="2"/>
+        <v>-9.1416666666666675</v>
       </c>
       <c r="P32">
         <v>0.04</v>
@@ -2262,29 +2496,45 @@
         <v>8</v>
       </c>
       <c r="S32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.23</v>
       </c>
       <c r="T32">
+        <f t="shared" si="4"/>
+        <v>0.02</v>
+      </c>
+      <c r="V32" s="1">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="W32" s="1">
+        <f t="shared" si="1"/>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N33">
         <f t="shared" si="2"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="N33">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V33" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W33" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -2310,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>-28</v>
+        <v>-20</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2319,8 +2569,8 @@
         <v>800</v>
       </c>
       <c r="N34">
-        <f t="shared" si="0"/>
-        <v>-4.6933333333333342</v>
+        <f t="shared" si="2"/>
+        <v>-4.666666666666667</v>
       </c>
       <c r="P34">
         <v>0.04</v>
@@ -2329,15 +2579,23 @@
         <v>5.5118099999999997</v>
       </c>
       <c r="S34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.17</v>
       </c>
       <c r="T34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="1">
+        <f t="shared" si="0"/>
+        <v>-17.086650000000013</v>
+      </c>
+      <c r="W34" s="1">
+        <f t="shared" si="1"/>
+        <v>1182.91335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -2363,7 +2621,7 @@
         <v>0.02</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K35">
         <v>-0.1</v>
@@ -2372,8 +2630,8 @@
         <v>750</v>
       </c>
       <c r="N35">
-        <f t="shared" si="0"/>
-        <v>-4.1183333333333341</v>
+        <f t="shared" si="2"/>
+        <v>-4.0583333333333345</v>
       </c>
       <c r="P35">
         <v>0.04</v>
@@ -2382,29 +2640,45 @@
         <v>6.6929100000000004</v>
       </c>
       <c r="S35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
       <c r="T35">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="V35" s="1">
+        <f t="shared" si="0"/>
+        <v>24.251850000000012</v>
+      </c>
+      <c r="W35" s="1">
+        <f t="shared" si="1"/>
+        <v>1224.2518500000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N36">
         <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="N36">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V36" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W36" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -2436,22 +2710,30 @@
         <v>1500</v>
       </c>
       <c r="N37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11.66</v>
       </c>
       <c r="P37">
         <v>0.03</v>
       </c>
       <c r="S37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.03</v>
       </c>
       <c r="T37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.04</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V37" s="1">
+        <f t="shared" si="0"/>
+        <v>-210</v>
+      </c>
+      <c r="W37" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -2483,7 +2765,7 @@
         <v>1200</v>
       </c>
       <c r="N38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8.4350000000000005</v>
       </c>
       <c r="P38">
@@ -2493,15 +2775,23 @@
         <v>4.5</v>
       </c>
       <c r="S38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="T38">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
+        <f t="shared" si="0"/>
+        <v>-52.5</v>
+      </c>
+      <c r="W38" s="1">
+        <f t="shared" si="1"/>
+        <v>1147.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -2533,7 +2823,7 @@
         <v>1500</v>
       </c>
       <c r="N39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15.353333333333333</v>
       </c>
       <c r="P39">
@@ -2543,15 +2833,23 @@
         <v>6.0236200000000002</v>
       </c>
       <c r="S39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.17</v>
       </c>
       <c r="T39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V39" s="1">
+        <f t="shared" si="0"/>
+        <v>0.82670000000000687</v>
+      </c>
+      <c r="W39" s="1">
+        <f t="shared" si="1"/>
+        <v>1200.8267000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2583,7 +2881,7 @@
         <v>3000</v>
       </c>
       <c r="N40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-12.683333333333334</v>
       </c>
       <c r="P40">
@@ -2593,12 +2891,20 @@
         <v>15.984252</v>
       </c>
       <c r="S40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.41</v>
       </c>
       <c r="T40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.09</v>
+      </c>
+      <c r="V40" s="1">
+        <f t="shared" si="0"/>
+        <v>349.44882000000001</v>
+      </c>
+      <c r="W40" s="1">
+        <f t="shared" si="1"/>
+        <v>1549.4488200000001</v>
       </c>
     </row>
   </sheetData>
